--- a/out/Attention_Base_repeat_4_000008.xlsx
+++ b/out/Attention_Base_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>-9.967563975858503e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>-0.1145081656113817</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>-0.1146078412511403</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>-0.1146960627441485</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0.3172241404946977</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0.5203618146902322</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0.02260218999342599</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0.2478326775253811</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0.03963641188544194</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0.3044960253665988</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0.04815355941771563</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0.3611633283758911</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0.01274263831885995</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0.3384332722624065</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0.007077841851105633</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0.3398353830484394</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0.01487426130114241</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0.3625137745640571</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0.005839641310941763</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0.359308325840154</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0.004157268481173275</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0.3617813006956056</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0.001633974677006633</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0.3608870158836842</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0.0009244721397067098</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0.3611025728676343</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0.00034965950766588</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0.3608751340597123</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0.000161245026955842</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0.3608477123296491</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>5.554939707654808e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0.3607982345370955</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>1.312545856304208e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0.3607680702722911</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0.3607630561240923</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0.3607587472467749</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0.36075557962521</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0.3607502102982222</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0.3607442175647919</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0.3607388497762135</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0.3607388865247052</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0.3607389967701808</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0.3607390702671644</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.3607392540096235</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0.36074079744628</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.3607422673859531</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0.3607435168346751</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0.3607448765288724</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0.3607426716193631</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0.3607422673859531</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3607414221706411</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0.3607419733980184</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0.360741642661592</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0.3607413486736575</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3607414221706411</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.3607409811887392</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0.3607408709432636</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0.3607408341947719</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0.3607409811887392</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0.3607405034583455</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0.3607414589191328</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0.3607414221706411</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0.3607410914342147</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0.3607415324161167</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0.3607409076917555</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0.3607407239492964</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0.3607403197158864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.3607394745005744</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0.3607394377520827</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.3607395847460499</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.3607395112490663</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0.3607395847460499</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0.3607396214945419</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0.3607395112490663</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0.3607399522309683</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0.3607398419854927</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0.3607398052370008</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0.3607397317400172</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0.3607396949915255</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-7.158570929792917</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0.3607394745005744</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-7.158570929792917</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0.3607394010035908</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-7.158570929792917</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0.3607393275066071</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-7.158570929792917</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.3607393642550991</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-7.158570929792917</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0.3607392540096235</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.01422621125862816</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0.3607393642550991</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>0.5857737887413719</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0.3607396582430336</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000008.xlsx
+++ b/out/Attention_Base_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.315708769287449e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1070196012911481</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1071127583788411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.107195290178011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2967655539730406</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4869056184988809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0211444468266281</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2319529869918532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03708028369412986</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2849619779636297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04504816554161525</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3379744971440681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0119208732929875</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3167105636086252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00662071862793783</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3180218968864733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01391396089809551</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3392374891218566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005462997413779955</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.336238264329596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003889903535221407</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3385515840686287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001528059163496676</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.337714767537842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008643570261933406</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3379160715260736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003261721230522456</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3377029962801158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001502354225216803</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3376769859358545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.232009589913218e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3376301586008151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3376016502520689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3375966368485123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.337592291222703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3375889408679101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3375835715409224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3375775788074921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3375722110189137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3375722477674054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3375723580128809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3375724315098645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3375741586889802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3375768780773752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3375782377715725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3375760328620633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3375756286286533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3375753346407185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3375750039042921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3375747099163576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3375742321859638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3375741954374721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3375743424314393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3375738647010457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.337574820161833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3375747834133413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3375744526769149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3375748936588168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3375742689344557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3375740851919966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3375736809585865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3375727989947828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3375729459887501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.337572982737242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3375728724917665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3375733134736684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3375732032281928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3375731664797009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3375730929827173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3375730562342256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3375728357432745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3375727622462909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3375726887493073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3375726152523237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3375727254977992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3375730194857337</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000008.xlsx
+++ b/out/Attention_Base_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.008622005581855774</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01018696930259466</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.51</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.01274324581027031</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01748831197619438</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01875213533639908</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.017723698168993</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.01648776605725288</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.01544623076915741</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01450853049755096</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01397688034921885</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01334821619093418</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.01279556378722191</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01240327209234238</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01196902990341187</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01129958033561707</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01130719948559999</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01101683545857668</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01077364385128021</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01054534036666155</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01033681351691484</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.01007105596363544</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.009909620508551598</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.00973968394100666</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.009610394015908241</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.009517466649413109</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.009400911629199982</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.009337540715932846</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.009213346987962723</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.009073151275515556</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.009021863341331482</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.009074123576283455</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.009326733648777008</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.009342595934867859</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.009309595450758934</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.009250573813915253</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.009204655885696411</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.009122127667069435</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.009027209132909775</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.009022919461131096</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.008972151204943657</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.008998123928904533</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.009037375450134277</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.009216789156198502</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.009250324219465256</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-9.315708769287449e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.1070196012911481</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.009547948837280273</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.009777656756341457</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.009811641648411751</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.009847692213952541</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.009825705550611019</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.009786405600607395</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.009717352688312531</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.009705566801130772</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.00964842177927494</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009648740291595459</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.009620983153581619</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.009586106985807419</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.009584946557879448</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.009719295427203178</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>-0.1071795241174268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.2400743906842873</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.009787771850824356</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.373430208872485</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.01710524993121548</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.009863516315817833</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.1671812123770492</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.02999678025955109</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0100337415933609</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.2100638145458303</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.03644223363718525</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01013029180467129</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.2529492714998109</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.00964284430385446</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01011665910482407</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.2357464238146958</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.005355008258813494</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01035647466778755</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.2368063050977331</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.01125502318500417</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01060187630355358</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.2539683543553441</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.004419051949620858</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01093424670398235</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.2515410520328716</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>0.003144731556826523</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01103560999035835</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.2534113458932778</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>0.001234754664546028</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01120467856526375</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.2527333048099468</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>0.0006994258173233274</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01129676774144173</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.2528953206828511</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>0.0002627561845954326</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01139380410313606</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.2527220192634754</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>0.0001205094905494436</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0113513395190239</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.2527000181027353</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>4.101754177817654e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01134398020803928</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.2526611444232901</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01131278276443481</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.2526369401159393</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0112354401499033</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.2526319296909508</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01113725826144218</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.2526274753971465</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01101920939981937</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.2526239412998946</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01096205972135067</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.2526186454698904</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01094643957912922</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.2526129834728867</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01088954694569111</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.2526127997304276</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01086082682013512</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.2526128364789192</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01075535640120506</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.2526129467243948</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01066466420888901</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.2526130202213784</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01048916671425104</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.2526132039638376</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01036833319813013</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.2526147474004941</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.009874606505036354</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.2526162173401671</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.009435867890715599</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.2526174667888891</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.008598307147622108</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.2526188264830864</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.009852683171629906</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.2526166215735772</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01042450964450836</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.2526162173401671</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01121377758681774</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.2526153721248552</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01163880340754986</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.2526159233522324</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01211434043943882</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.252615592615806</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0123359365388751</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.2526152986278716</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01276012137532234</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.2526153721248552</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01312385499477386</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.2526149311429532</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0132831297814846</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.2526148208974777</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01319808140397072</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.252614784148986</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01344987004995346</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.2526149311429532</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01301497779786587</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.2526144534125596</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01261858828365803</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.2526154088733469</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01361641846597195</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.2526153721248552</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01399854384362698</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.2526150413884288</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0140448771417141</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.2526154823703307</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01465925201773643</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.2526148576459696</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0149727500975132</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.2526146739035104</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01563744992017746</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.2526142696701004</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01644901372492313</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.2526134244547885</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01642287522554398</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.2526133877062968</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01633851043879986</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.252613534700264</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01629630662500858</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.2526134612032804</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01563177444040775</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.252613534700264</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01630565896630287</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.2526135714487559</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01589550264179707</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.2526134612032804</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01590200141072273</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.2526139021851823</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.01582301594316959</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.2526137919397068</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01596813462674618</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.2526137551912149</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01594603434205055</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.2526136816942312</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01601424813270569</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.2526136449457395</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01625597476959229</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.2526134244547885</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0160084068775177</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.2526133509578048</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01612424477934837</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.2526132774608212</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01602731086313725</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.2526133142093132</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0158361904323101</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.2526132039638376</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01518260315060616</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.2526133142093132</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01492370665073395</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.2526136081972476</v>
       </c>
     </row>
   </sheetData>
